--- a/Summer26PrepTANeeds.xlsx
+++ b/Summer26PrepTANeeds.xlsx
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Crystal Violet</t>
+          <t>Congo Red</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr"/>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Methylene Blue</t>
+          <t>Maneval Solution</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Nigrosin</t>
+          <t>Methylene Blue</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>VP A</t>
+          <t>Nitrate reagent A</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr"/>
@@ -15186,11 +15186,7 @@
       <c r="G378" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="H378" s="5" t="inlineStr">
-        <is>
-          <t>estimation, need more accurate data</t>
-        </is>
-      </c>
+      <c r="H378" s="5" t="inlineStr"/>
       <c r="I378" s="4" t="inlineStr">
         <is>
           <t>No Prep Needed</t>
@@ -15213,7 +15209,7 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>VP B</t>
+          <t>Nitrate reagent B</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr"/>
@@ -15225,11 +15221,7 @@
       <c r="G379" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="H379" s="5" t="inlineStr">
-        <is>
-          <t>estimation, need more accurate data</t>
-        </is>
-      </c>
+      <c r="H379" s="5" t="inlineStr"/>
       <c r="I379" s="4" t="inlineStr">
         <is>
           <t>No Prep Needed</t>
@@ -15252,22 +15244,26 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>VP A</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr"/>
       <c r="F380" s="4" t="inlineStr">
         <is>
-          <t>microcetrifuge_tube</t>
+          <t>1_ml</t>
         </is>
       </c>
       <c r="G380" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="H380" s="5" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H380" s="5" t="inlineStr">
+        <is>
+          <t>estimation, need more accurate data</t>
+        </is>
+      </c>
       <c r="I380" s="4" t="inlineStr">
         <is>
-          <t>Prep TA</t>
+          <t>No Prep Needed</t>
         </is>
       </c>
       <c r="J380" s="5" t="inlineStr"/>
@@ -15287,19 +15283,23 @@
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>Zinc Powder</t>
+          <t>VP B</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr"/>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>1_ml</t>
         </is>
       </c>
       <c r="G381" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="H381" s="5" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H381" s="5" t="inlineStr">
+        <is>
+          <t>estimation, need more accurate data</t>
+        </is>
+      </c>
       <c r="I381" s="4" t="inlineStr">
         <is>
           <t>No Prep Needed</t>
@@ -15322,26 +15322,22 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>Zinc Powder</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr"/>
       <c r="F382" s="4" t="inlineStr">
         <is>
-          <t>premade</t>
+          <t>microcetrifuge_tube</t>
         </is>
       </c>
       <c r="G382" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="H382" s="5" t="inlineStr">
-        <is>
-          <t>have it as number of uses</t>
-        </is>
-      </c>
+      <c r="H382" s="5" t="inlineStr"/>
       <c r="I382" s="4" t="inlineStr">
         <is>
-          <t>No Prep Needed</t>
+          <t>Prep TA</t>
         </is>
       </c>
       <c r="J382" s="5" t="inlineStr"/>
@@ -15356,12 +15352,12 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>Empty Petri Dish, 100mm</t>
+          <t>Zinc Powder</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr"/>
@@ -15371,12 +15367,12 @@
         </is>
       </c>
       <c r="G383" s="4" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="H383" s="5" t="inlineStr"/>
       <c r="I383" s="4" t="inlineStr">
         <is>
-          <t>Prep TA</t>
+          <t>No Prep Needed</t>
         </is>
       </c>
       <c r="J383" s="5" t="inlineStr"/>
@@ -15391,26 +15387,26 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>Nitrate reagent A</t>
+          <t>Zinc Powder</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr"/>
       <c r="F384" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>premade</t>
         </is>
       </c>
       <c r="G384" s="4" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H384" s="5" t="inlineStr">
         <is>
-          <t>noted as bottles used</t>
+          <t>have it as number of uses</t>
         </is>
       </c>
       <c r="I384" s="4" t="inlineStr">
@@ -15435,7 +15431,7 @@
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>Nitrate reagent B</t>
+          <t>Empty Petri Dish, 100mm</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr"/>
@@ -15445,16 +15441,12 @@
         </is>
       </c>
       <c r="G385" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H385" s="5" t="inlineStr">
-        <is>
-          <t>noted as bottles used</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H385" s="5" t="inlineStr"/>
       <c r="I385" s="4" t="inlineStr">
         <is>
-          <t>No Prep Needed</t>
+          <t>Prep TA</t>
         </is>
       </c>
       <c r="J385" s="5" t="inlineStr"/>
@@ -25401,7 +25393,7 @@
       </c>
       <c r="D641" s="5" t="inlineStr">
         <is>
-          <t>VP A</t>
+          <t>Nitrate reagent A</t>
         </is>
       </c>
       <c r="E641" s="4" t="inlineStr"/>
@@ -25411,11 +25403,11 @@
         </is>
       </c>
       <c r="G641" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H641" s="5" t="inlineStr">
         <is>
-          <t>just put bottles out, estimate 4 will be completely used up</t>
+          <t>just put bottles out, estimate 2ml per pair will be used</t>
         </is>
       </c>
       <c r="I641" s="4" t="inlineStr">
@@ -25440,7 +25432,7 @@
       </c>
       <c r="D642" s="5" t="inlineStr">
         <is>
-          <t>VP B</t>
+          <t>Nitrate reagent B</t>
         </is>
       </c>
       <c r="E642" s="4" t="inlineStr"/>
@@ -25450,11 +25442,11 @@
         </is>
       </c>
       <c r="G642" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H642" s="5" t="inlineStr">
         <is>
-          <t>just put bottles out, estimate 4 will be completely used up</t>
+          <t>just put bottles out, estimate 2ml per pair will be used</t>
         </is>
       </c>
       <c r="I642" s="4" t="inlineStr">
@@ -25479,7 +25471,7 @@
       </c>
       <c r="D643" s="5" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>VP A</t>
         </is>
       </c>
       <c r="E643" s="4" t="inlineStr"/>
@@ -25489,12 +25481,16 @@
         </is>
       </c>
       <c r="G643" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H643" s="5" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="H643" s="5" t="inlineStr">
+        <is>
+          <t>just put bottles out, estimate 4 will be completely used up</t>
+        </is>
+      </c>
       <c r="I643" s="4" t="inlineStr">
         <is>
-          <t>Prep TA</t>
+          <t>No Prep Needed</t>
         </is>
       </c>
       <c r="J643" s="5" t="inlineStr"/>
@@ -25514,22 +25510,26 @@
       </c>
       <c r="D644" s="5" t="inlineStr">
         <is>
-          <t>Saline (0.85% NaCl)</t>
+          <t>VP B</t>
         </is>
       </c>
       <c r="E644" s="4" t="inlineStr"/>
       <c r="F644" s="4" t="inlineStr">
         <is>
-          <t>broth</t>
+          <t>1_ml</t>
         </is>
       </c>
       <c r="G644" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H644" s="5" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="H644" s="5" t="inlineStr">
+        <is>
+          <t>just put bottles out, estimate 4 will be completely used up</t>
+        </is>
+      </c>
       <c r="I644" s="4" t="inlineStr">
         <is>
-          <t>Prep TA</t>
+          <t>No Prep Needed</t>
         </is>
       </c>
       <c r="J644" s="5" t="inlineStr"/>
@@ -25549,13 +25549,13 @@
       </c>
       <c r="D645" s="5" t="inlineStr">
         <is>
-          <t>Kovac's Reagent</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="E645" s="4" t="inlineStr"/>
       <c r="F645" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>1_ml</t>
         </is>
       </c>
       <c r="G645" s="4" t="n">
@@ -25564,7 +25564,7 @@
       <c r="H645" s="5" t="inlineStr"/>
       <c r="I645" s="4" t="inlineStr">
         <is>
-          <t>No Prep Needed</t>
+          <t>Prep TA</t>
         </is>
       </c>
       <c r="J645" s="5" t="inlineStr"/>
@@ -25584,26 +25584,22 @@
       </c>
       <c r="D646" s="5" t="inlineStr">
         <is>
-          <t>Zinc Powder</t>
+          <t>Saline (0.85% NaCl)</t>
         </is>
       </c>
       <c r="E646" s="4" t="inlineStr"/>
       <c r="F646" s="4" t="inlineStr">
         <is>
-          <t>premade</t>
+          <t>broth</t>
         </is>
       </c>
       <c r="G646" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H646" s="5" t="inlineStr">
-        <is>
-          <t>put out bottles</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="H646" s="5" t="inlineStr"/>
       <c r="I646" s="4" t="inlineStr">
         <is>
-          <t>No Prep Needed</t>
+          <t>Prep TA</t>
         </is>
       </c>
       <c r="J646" s="5" t="inlineStr"/>
@@ -25613,17 +25609,17 @@
       <c r="A647" s="6" t="n"/>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>140L</t>
+          <t>351L</t>
         </is>
       </c>
       <c r="C647" s="4" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="D647" s="5" t="inlineStr">
         <is>
-          <t>Sterile Cotton Swabs</t>
+          <t>Kovac's Reagent</t>
         </is>
       </c>
       <c r="E647" s="4" t="inlineStr"/>
@@ -25633,13 +25629,9 @@
         </is>
       </c>
       <c r="G647" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="H647" s="5" t="inlineStr">
-        <is>
-          <t>estimation, need more accurate data</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H647" s="5" t="inlineStr"/>
       <c r="I647" s="4" t="inlineStr">
         <is>
           <t>No Prep Needed</t>
@@ -25657,18 +25649,18 @@
       </c>
       <c r="C648" s="4" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="D648" s="5" t="inlineStr">
         <is>
-          <t>Nitrate reagent A</t>
+          <t>Zinc Powder</t>
         </is>
       </c>
       <c r="E648" s="4" t="inlineStr"/>
       <c r="F648" s="4" t="inlineStr">
         <is>
-          <t>1_ml</t>
+          <t>premade</t>
         </is>
       </c>
       <c r="G648" s="4" t="n">
@@ -25676,7 +25668,7 @@
       </c>
       <c r="H648" s="5" t="inlineStr">
         <is>
-          <t>just put bottles out, estimate 2ml per pair will be used</t>
+          <t>put out bottles</t>
         </is>
       </c>
       <c r="I648" s="4" t="inlineStr">
@@ -25691,7 +25683,7 @@
       <c r="A649" s="6" t="n"/>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>351L</t>
+          <t>140L</t>
         </is>
       </c>
       <c r="C649" s="4" t="inlineStr">
@@ -25701,21 +25693,21 @@
       </c>
       <c r="D649" s="5" t="inlineStr">
         <is>
-          <t>Nitrate reagent B</t>
+          <t>Sterile Cotton Swabs</t>
         </is>
       </c>
       <c r="E649" s="4" t="inlineStr"/>
       <c r="F649" s="4" t="inlineStr">
         <is>
-          <t>1_ml</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G649" s="4" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="H649" s="5" t="inlineStr">
         <is>
-          <t>just put bottles out, estimate 2ml per pair will be used</t>
+          <t>estimation, need more accurate data</t>
         </is>
       </c>
       <c r="I649" s="4" t="inlineStr">
